--- a/設計資料/設計資料.xlsx
+++ b/設計資料/設計資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucel\Documents\PythonStudy\AirlineProject\設計資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE725A5-9E9D-44F0-9452-FB3C2410399F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34112A2-FC66-4160-959C-5ACCACE58301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="18195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="18195" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="入力レイアウト" sheetId="5" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1693,12 +1693,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1919,7 +1913,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2085,30 +2079,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2127,23 +2097,42 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2615,18 +2604,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="86" customFormat="1" ht="7.25" customHeight="1">
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="87"/>
-    </row>
+    <row r="6" spans="1:11" s="77" customFormat="1" ht="7.25" customHeight="1"/>
     <row r="7" spans="1:11">
       <c r="A7" s="28" t="s">
         <v>262</v>
@@ -2697,7 +2675,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="86" customFormat="1" ht="7.5" customHeight="1" thickBot="1"/>
+    <row r="9" spans="1:11" s="77" customFormat="1" ht="7.5" customHeight="1" thickBot="1"/>
     <row r="10" spans="1:11" ht="15.75" thickTop="1" thickBot="1">
       <c r="B10" s="38" t="s">
         <v>279</v>
@@ -2720,10 +2698,10 @@
       <c r="H10" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="I10" s="79" t="s">
+      <c r="I10" s="71" t="s">
         <v>212</v>
       </c>
-      <c r="J10" s="79" t="s">
+      <c r="J10" s="71" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2739,7 +2717,7 @@
       <c r="H11" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="I11" s="80" t="s">
+      <c r="I11" s="72" t="s">
         <v>306</v>
       </c>
       <c r="J11" s="32"/>
@@ -2762,7 +2740,7 @@
       </c>
       <c r="H12" s="31"/>
       <c r="J12" s="31"/>
-      <c r="K12" s="80" t="s">
+      <c r="K12" s="72" t="s">
         <v>214</v>
       </c>
     </row>
@@ -2788,7 +2766,7 @@
       <c r="H13" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="I13" s="79" t="s">
+      <c r="I13" s="71" t="s">
         <v>215</v>
       </c>
     </row>
@@ -2801,10 +2779,10 @@
       <c r="G14" s="42"/>
       <c r="H14" s="32"/>
       <c r="I14" s="31"/>
-      <c r="J14" s="80" t="s">
+      <c r="J14" s="72" t="s">
         <v>247</v>
       </c>
-      <c r="K14" s="80" t="s">
+      <c r="K14" s="72" t="s">
         <v>247</v>
       </c>
     </row>
@@ -2840,15 +2818,15 @@
       <c r="H18" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="J18" s="80" t="s">
+      <c r="J18" s="72" t="s">
         <v>219</v>
       </c>
-      <c r="K18" s="80" t="s">
+      <c r="K18" s="72" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="15.75" thickTop="1" thickBot="1">
-      <c r="I19" s="80" t="s">
+      <c r="I19" s="72" t="s">
         <v>220</v>
       </c>
     </row>
@@ -2869,10 +2847,10 @@
       <c r="H20" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="J20" s="80" t="s">
+      <c r="J20" s="72" t="s">
         <v>221</v>
       </c>
-      <c r="K20" s="80" t="s">
+      <c r="K20" s="72" t="s">
         <v>221</v>
       </c>
     </row>
@@ -2893,10 +2871,10 @@
       <c r="H21" s="37" t="s">
         <v>222</v>
       </c>
-      <c r="J21" s="83" t="s">
+      <c r="J21" s="75" t="s">
         <v>222</v>
       </c>
-      <c r="K21" s="80" t="s">
+      <c r="K21" s="72" t="s">
         <v>222</v>
       </c>
     </row>
@@ -2927,7 +2905,7 @@
       <c r="G23" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="K23" s="80" t="s">
+      <c r="K23" s="72" t="s">
         <v>224</v>
       </c>
     </row>
@@ -2976,13 +2954,13 @@
       <c r="F29" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="H29" s="81" t="s">
+      <c r="H29" s="73" t="s">
         <v>132</v>
       </c>
-      <c r="I29" s="82" t="s">
+      <c r="I29" s="74" t="s">
         <v>229</v>
       </c>
-      <c r="J29" s="82" t="s">
+      <c r="J29" s="74" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3007,7 +2985,7 @@
       </c>
       <c r="H30" s="31"/>
       <c r="J30" s="31"/>
-      <c r="K30" s="84" t="s">
+      <c r="K30" s="76" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3032,7 +3010,7 @@
       </c>
       <c r="H31" s="31"/>
       <c r="J31" s="31"/>
-      <c r="K31" s="84" t="s">
+      <c r="K31" s="76" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3078,7 +3056,7 @@
       <c r="H33" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="J33" s="82" t="s">
+      <c r="J33" s="74" t="s">
         <v>235</v>
       </c>
     </row>
@@ -3101,7 +3079,7 @@
       <c r="H34" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="J34" s="82" t="s">
+      <c r="J34" s="74" t="s">
         <v>236</v>
       </c>
     </row>
@@ -3122,28 +3100,28 @@
     </row>
     <row r="37" spans="2:11" ht="15.4" thickBot="1">
       <c r="H37" s="31"/>
-      <c r="I37" s="82" t="s">
+      <c r="I37" s="74" t="s">
         <v>231</v>
       </c>
       <c r="J37" s="31"/>
     </row>
     <row r="38" spans="2:11" ht="15.4" thickBot="1">
       <c r="H38" s="31"/>
-      <c r="I38" s="82" t="s">
+      <c r="I38" s="74" t="s">
         <v>232</v>
       </c>
       <c r="J38" s="31"/>
     </row>
     <row r="39" spans="2:11" ht="15.4" thickBot="1">
       <c r="H39" s="31"/>
-      <c r="I39" s="82" t="s">
+      <c r="I39" s="74" t="s">
         <v>233</v>
       </c>
       <c r="J39" s="31"/>
     </row>
     <row r="40" spans="2:11" ht="15.4" thickBot="1">
       <c r="H40" s="31"/>
-      <c r="I40" s="82" t="s">
+      <c r="I40" s="74" t="s">
         <v>234</v>
       </c>
       <c r="J40" s="31"/>
@@ -3189,13 +3167,13 @@
       <c r="H42" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="I42" s="79" t="s">
+      <c r="I42" s="71" t="s">
         <v>238</v>
       </c>
-      <c r="J42" s="79" t="s">
+      <c r="J42" s="71" t="s">
         <v>238</v>
       </c>
-      <c r="K42" s="79" t="s">
+      <c r="K42" s="71" t="s">
         <v>238</v>
       </c>
     </row>
@@ -3205,17 +3183,17 @@
       </c>
     </row>
     <row r="44" spans="2:11" ht="15.4" thickTop="1">
-      <c r="K44" s="93" t="s">
+      <c r="K44" s="89" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="45" spans="2:11" ht="15.4" thickBot="1">
-      <c r="K45" s="93" t="s">
+      <c r="K45" s="89" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="46" spans="2:11" ht="15.4" thickBot="1">
-      <c r="K46" s="85" t="s">
+      <c r="K46" s="90" t="s">
         <v>249</v>
       </c>
     </row>
@@ -3228,7 +3206,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF626530-5038-4909-824C-1D736B82CFEE}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="B1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="28"/>
@@ -3238,8 +3216,8 @@
     <col min="8" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30">
-      <c r="B1" s="90" t="s">
+    <row r="1" spans="2:7" ht="30">
+      <c r="B1" s="80" t="s">
         <v>332</v>
       </c>
       <c r="C1" s="27" t="s">
@@ -3248,7 +3226,7 @@
       <c r="D1" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="90" t="s">
+      <c r="E1" s="80" t="s">
         <v>331</v>
       </c>
       <c r="F1" s="27" t="s">
@@ -3258,7 +3236,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="2:7">
       <c r="B2" s="29" t="s">
         <v>330</v>
       </c>
@@ -3278,396 +3256,332 @@
         <v>323</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="86" customFormat="1">
-      <c r="B3" s="88"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="91"/>
-      <c r="B4" s="92" t="s">
+    <row r="3" spans="2:7" s="77" customFormat="1">
+      <c r="B3" s="78"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="B4" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="C4" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="D4" s="92" t="s">
+      <c r="D4" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="92" t="s">
+      <c r="E4" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="F4" s="92" t="s">
+      <c r="F4" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="G4" s="91"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="91"/>
-      <c r="B5" s="92" t="s">
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="E5" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="F5" s="92" t="s">
+      <c r="F5" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="G5" s="92" t="s">
+      <c r="G5" s="31" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="91"/>
-      <c r="B6" s="92" t="s">
+    <row r="6" spans="2:7">
+      <c r="B6" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92" t="s">
+      <c r="C6" s="31"/>
+      <c r="D6" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92" t="s">
+    <row r="7" spans="2:7">
+      <c r="B7" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C7" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="D7" s="92" t="s">
+      <c r="D7" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="E7" s="92" t="s">
+      <c r="E7" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="F7" s="92" t="s">
+      <c r="F7" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="G7" s="92" t="s">
+      <c r="G7" s="31" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="91"/>
-      <c r="B8" s="92" t="s">
+    <row r="8" spans="2:7">
+      <c r="B8" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="D8" s="92" t="s">
+      <c r="D8" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="E8" s="92" t="s">
+      <c r="E8" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="F8" s="92" t="s">
+      <c r="F8" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="G8" s="92" t="s">
+      <c r="G8" s="31" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="91"/>
-      <c r="B9" s="92" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="91" t="s">
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="28" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="91"/>
-      <c r="B10" s="92" t="s">
+    <row r="10" spans="2:7">
+      <c r="B10" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="C10" s="92"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="91" t="s">
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="28" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="91"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="92" t="s">
+    <row r="11" spans="2:7">
+      <c r="C11" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="D11" s="92"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="91"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="91"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="92" t="s">
+      <c r="D11" s="31"/>
+      <c r="F11" s="31"/>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="C12" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="91"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="91"/>
-      <c r="B13" s="92" t="s">
+      <c r="F12" s="31"/>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="92" t="s">
+      <c r="D13" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="E13" s="92" t="s">
+      <c r="E13" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="F13" s="92" t="s">
+      <c r="F13" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="G13" s="91" t="s">
+      <c r="G13" s="28" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="91"/>
-      <c r="B14" s="92" t="s">
+    <row r="14" spans="2:7">
+      <c r="B14" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="92" t="s">
+      <c r="C14" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="D14" s="92" t="s">
+      <c r="D14" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="E14" s="92" t="s">
+      <c r="E14" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="F14" s="92" t="s">
+      <c r="F14" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="91" t="s">
+      <c r="G14" s="28" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="91"/>
-      <c r="B15" s="92" t="s">
+    <row r="15" spans="2:7">
+      <c r="B15" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="92" t="s">
+      <c r="C15" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="92" t="s">
+      <c r="D15" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="F15" s="92" t="s">
+      <c r="F15" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="G15" s="91"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="91"/>
-      <c r="B16" s="92" t="s">
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="91"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="91"/>
-      <c r="B17" s="92" t="s">
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="92" t="s">
+      <c r="D17" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="91" t="s">
+      <c r="E17" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="F17" s="91" t="s">
+      <c r="F17" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="G17" s="91" t="s">
+      <c r="G17" s="28" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="91"/>
-      <c r="B18" s="92" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="C18" s="92" t="s">
+      <c r="C18" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="D18" s="92" t="s">
+      <c r="D18" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="E18" s="91" t="s">
+      <c r="E18" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="F18" s="91" t="s">
+      <c r="F18" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G18" s="91" t="s">
+      <c r="G18" s="28" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="91"/>
-      <c r="B19" s="92" t="s">
+    <row r="19" spans="2:7">
+      <c r="B19" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="C19" s="91"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="91"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="91"/>
-      <c r="B20" s="92" t="s">
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="92" t="s">
+      <c r="C20" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="92" t="s">
+      <c r="D20" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="E20" s="91" t="s">
+      <c r="E20" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="91" t="s">
+      <c r="F20" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="G20" s="91"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92" t="s">
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="C21" s="92" t="s">
+      <c r="C21" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="D21" s="92" t="s">
+      <c r="D21" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="E21" s="92" t="s">
+      <c r="E21" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="F21" s="92" t="s">
+      <c r="F21" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="G21" s="91"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="91"/>
-      <c r="B22" s="92" t="s">
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="C22" s="92" t="s">
+      <c r="C22" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="92" t="s">
+      <c r="D22" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="E22" s="92" t="s">
+      <c r="E22" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="F22" s="92" t="s">
+      <c r="F22" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="G22" s="91"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92" t="s">
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="91"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="91"/>
-      <c r="B24" s="91"/>
-      <c r="C24" s="91"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91" t="s">
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="G24" s="28" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="91" t="s">
+    <row r="25" spans="2:7">
+      <c r="B25" s="31"/>
+      <c r="G25" s="28" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="91" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="31"/>
+      <c r="G26" s="28" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="91"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="91" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="31"/>
+      <c r="G27" s="28" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="2:7">
       <c r="B28" s="31" t="s">
         <v>238</v>
       </c>
@@ -3871,62 +3785,62 @@
     <row r="2" spans="1:50" ht="17.649999999999999" customHeight="1">
       <c r="A2" s="48"/>
       <c r="B2" s="48"/>
-      <c r="C2" s="71" t="s">
+      <c r="C2" s="84" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="71" t="s">
+      <c r="D2" s="85"/>
+      <c r="E2" s="84" t="s">
         <v>180</v>
       </c>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="72"/>
-      <c r="Y2" s="73"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="85"/>
+      <c r="T2" s="85"/>
+      <c r="U2" s="85"/>
+      <c r="V2" s="85"/>
+      <c r="W2" s="85"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="86"/>
       <c r="Z2" s="49"/>
       <c r="AA2" s="49"/>
       <c r="AB2" s="49"/>
       <c r="AC2" s="49"/>
       <c r="AD2" s="49"/>
       <c r="AE2" s="49"/>
-      <c r="AF2" s="71" t="s">
+      <c r="AF2" s="84" t="s">
         <v>179</v>
       </c>
-      <c r="AG2" s="72"/>
-      <c r="AH2" s="72"/>
-      <c r="AI2" s="72"/>
-      <c r="AJ2" s="72"/>
-      <c r="AK2" s="72"/>
-      <c r="AL2" s="73"/>
-      <c r="AM2" s="74" t="s">
+      <c r="AG2" s="85"/>
+      <c r="AH2" s="85"/>
+      <c r="AI2" s="85"/>
+      <c r="AJ2" s="85"/>
+      <c r="AK2" s="85"/>
+      <c r="AL2" s="86"/>
+      <c r="AM2" s="87" t="s">
         <v>178</v>
       </c>
-      <c r="AN2" s="75"/>
-      <c r="AO2" s="75"/>
-      <c r="AP2" s="75"/>
-      <c r="AQ2" s="75"/>
-      <c r="AR2" s="75"/>
-      <c r="AS2" s="75"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="75"/>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="75"/>
-      <c r="AX2" s="75"/>
+      <c r="AN2" s="88"/>
+      <c r="AO2" s="88"/>
+      <c r="AP2" s="88"/>
+      <c r="AQ2" s="88"/>
+      <c r="AR2" s="88"/>
+      <c r="AS2" s="88"/>
+      <c r="AT2" s="88"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
+      <c r="AW2" s="88"/>
+      <c r="AX2" s="88"/>
     </row>
     <row r="3" spans="1:50">
       <c r="A3" s="50" t="s">
@@ -5473,20 +5387,20 @@
       <c r="AJ15" s="53"/>
       <c r="AK15" s="65"/>
       <c r="AL15" s="53"/>
-      <c r="AM15" s="76" t="s">
+      <c r="AM15" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="AN15" s="78"/>
-      <c r="AO15" s="78"/>
-      <c r="AP15" s="78"/>
-      <c r="AQ15" s="78"/>
-      <c r="AR15" s="78"/>
-      <c r="AS15" s="78"/>
-      <c r="AT15" s="78"/>
-      <c r="AU15" s="78"/>
-      <c r="AV15" s="78"/>
-      <c r="AW15" s="78"/>
-      <c r="AX15" s="78"/>
+      <c r="AN15" s="83"/>
+      <c r="AO15" s="83"/>
+      <c r="AP15" s="83"/>
+      <c r="AQ15" s="83"/>
+      <c r="AR15" s="83"/>
+      <c r="AS15" s="83"/>
+      <c r="AT15" s="83"/>
+      <c r="AU15" s="83"/>
+      <c r="AV15" s="83"/>
+      <c r="AW15" s="83"/>
+      <c r="AX15" s="83"/>
     </row>
     <row r="16" spans="1:50">
       <c r="B16" s="25" t="s">
@@ -5973,20 +5887,20 @@
       <c r="AJ19" s="53"/>
       <c r="AK19" s="65"/>
       <c r="AL19" s="53"/>
-      <c r="AM19" s="76" t="s">
+      <c r="AM19" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="AN19" s="77"/>
-      <c r="AO19" s="77"/>
-      <c r="AP19" s="77"/>
-      <c r="AQ19" s="77"/>
-      <c r="AR19" s="77"/>
-      <c r="AS19" s="77"/>
-      <c r="AT19" s="77"/>
-      <c r="AU19" s="77"/>
-      <c r="AV19" s="77"/>
-      <c r="AW19" s="77"/>
-      <c r="AX19" s="77"/>
+      <c r="AN19" s="82"/>
+      <c r="AO19" s="82"/>
+      <c r="AP19" s="82"/>
+      <c r="AQ19" s="82"/>
+      <c r="AR19" s="82"/>
+      <c r="AS19" s="82"/>
+      <c r="AT19" s="82"/>
+      <c r="AU19" s="82"/>
+      <c r="AV19" s="82"/>
+      <c r="AW19" s="82"/>
+      <c r="AX19" s="82"/>
     </row>
     <row r="20" spans="1:50">
       <c r="B20" s="25" t="s">
@@ -6473,20 +6387,20 @@
       <c r="AJ23" s="53"/>
       <c r="AK23" s="65"/>
       <c r="AL23" s="53"/>
-      <c r="AM23" s="76" t="s">
+      <c r="AM23" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="AN23" s="77"/>
-      <c r="AO23" s="77"/>
-      <c r="AP23" s="77"/>
-      <c r="AQ23" s="77"/>
-      <c r="AR23" s="77"/>
-      <c r="AS23" s="77"/>
-      <c r="AT23" s="77"/>
-      <c r="AU23" s="77"/>
-      <c r="AV23" s="77"/>
-      <c r="AW23" s="77"/>
-      <c r="AX23" s="77"/>
+      <c r="AN23" s="82"/>
+      <c r="AO23" s="82"/>
+      <c r="AP23" s="82"/>
+      <c r="AQ23" s="82"/>
+      <c r="AR23" s="82"/>
+      <c r="AS23" s="82"/>
+      <c r="AT23" s="82"/>
+      <c r="AU23" s="82"/>
+      <c r="AV23" s="82"/>
+      <c r="AW23" s="82"/>
+      <c r="AX23" s="82"/>
     </row>
     <row r="24" spans="1:50">
       <c r="B24" s="25" t="s">
@@ -6979,20 +6893,20 @@
       <c r="AJ27" s="53"/>
       <c r="AK27" s="65"/>
       <c r="AL27" s="53"/>
-      <c r="AM27" s="76" t="s">
+      <c r="AM27" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="AN27" s="77"/>
-      <c r="AO27" s="77"/>
-      <c r="AP27" s="77"/>
-      <c r="AQ27" s="77"/>
-      <c r="AR27" s="77"/>
-      <c r="AS27" s="77"/>
-      <c r="AT27" s="77"/>
-      <c r="AU27" s="77"/>
-      <c r="AV27" s="77"/>
-      <c r="AW27" s="77"/>
-      <c r="AX27" s="77"/>
+      <c r="AN27" s="82"/>
+      <c r="AO27" s="82"/>
+      <c r="AP27" s="82"/>
+      <c r="AQ27" s="82"/>
+      <c r="AR27" s="82"/>
+      <c r="AS27" s="82"/>
+      <c r="AT27" s="82"/>
+      <c r="AU27" s="82"/>
+      <c r="AV27" s="82"/>
+      <c r="AW27" s="82"/>
+      <c r="AX27" s="82"/>
     </row>
     <row r="28" spans="1:50">
       <c r="B28" s="25" t="s">
@@ -7485,20 +7399,20 @@
       <c r="AJ31" s="53"/>
       <c r="AK31" s="65"/>
       <c r="AL31" s="53"/>
-      <c r="AM31" s="76" t="s">
+      <c r="AM31" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="AN31" s="77"/>
-      <c r="AO31" s="77"/>
-      <c r="AP31" s="77"/>
-      <c r="AQ31" s="77"/>
-      <c r="AR31" s="77"/>
-      <c r="AS31" s="77"/>
-      <c r="AT31" s="77"/>
-      <c r="AU31" s="77"/>
-      <c r="AV31" s="77"/>
-      <c r="AW31" s="77"/>
-      <c r="AX31" s="77"/>
+      <c r="AN31" s="82"/>
+      <c r="AO31" s="82"/>
+      <c r="AP31" s="82"/>
+      <c r="AQ31" s="82"/>
+      <c r="AR31" s="82"/>
+      <c r="AS31" s="82"/>
+      <c r="AT31" s="82"/>
+      <c r="AU31" s="82"/>
+      <c r="AV31" s="82"/>
+      <c r="AW31" s="82"/>
+      <c r="AX31" s="82"/>
     </row>
     <row r="32" spans="1:50">
       <c r="B32" s="25" t="s">
@@ -7989,20 +7903,20 @@
       <c r="AJ35" s="53"/>
       <c r="AK35" s="65"/>
       <c r="AL35" s="53"/>
-      <c r="AM35" s="76" t="s">
+      <c r="AM35" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="AN35" s="77"/>
-      <c r="AO35" s="77"/>
-      <c r="AP35" s="77"/>
-      <c r="AQ35" s="77"/>
-      <c r="AR35" s="77"/>
-      <c r="AS35" s="77"/>
-      <c r="AT35" s="77"/>
-      <c r="AU35" s="77"/>
-      <c r="AV35" s="77"/>
-      <c r="AW35" s="77"/>
-      <c r="AX35" s="77"/>
+      <c r="AN35" s="82"/>
+      <c r="AO35" s="82"/>
+      <c r="AP35" s="82"/>
+      <c r="AQ35" s="82"/>
+      <c r="AR35" s="82"/>
+      <c r="AS35" s="82"/>
+      <c r="AT35" s="82"/>
+      <c r="AU35" s="82"/>
+      <c r="AV35" s="82"/>
+      <c r="AW35" s="82"/>
+      <c r="AX35" s="82"/>
     </row>
     <row r="36" spans="1:50">
       <c r="B36" s="25" t="s">
@@ -8495,20 +8409,20 @@
       <c r="AJ39" s="53"/>
       <c r="AK39" s="65"/>
       <c r="AL39" s="53"/>
-      <c r="AM39" s="76" t="s">
+      <c r="AM39" s="81" t="s">
         <v>293</v>
       </c>
-      <c r="AN39" s="77"/>
-      <c r="AO39" s="77"/>
-      <c r="AP39" s="77"/>
-      <c r="AQ39" s="77"/>
-      <c r="AR39" s="77"/>
-      <c r="AS39" s="77"/>
-      <c r="AT39" s="77"/>
-      <c r="AU39" s="77"/>
-      <c r="AV39" s="77"/>
-      <c r="AW39" s="77"/>
-      <c r="AX39" s="77"/>
+      <c r="AN39" s="82"/>
+      <c r="AO39" s="82"/>
+      <c r="AP39" s="82"/>
+      <c r="AQ39" s="82"/>
+      <c r="AR39" s="82"/>
+      <c r="AS39" s="82"/>
+      <c r="AT39" s="82"/>
+      <c r="AU39" s="82"/>
+      <c r="AV39" s="82"/>
+      <c r="AW39" s="82"/>
+      <c r="AX39" s="82"/>
     </row>
     <row r="40" spans="1:50">
       <c r="B40" s="25" t="s">
@@ -9001,20 +8915,20 @@
       <c r="AJ43" s="53"/>
       <c r="AK43" s="65"/>
       <c r="AL43" s="53"/>
-      <c r="AM43" s="76" t="s">
+      <c r="AM43" s="81" t="s">
         <v>296</v>
       </c>
-      <c r="AN43" s="77"/>
-      <c r="AO43" s="77"/>
-      <c r="AP43" s="77"/>
-      <c r="AQ43" s="77"/>
-      <c r="AR43" s="77"/>
-      <c r="AS43" s="77"/>
-      <c r="AT43" s="77"/>
-      <c r="AU43" s="77"/>
-      <c r="AV43" s="77"/>
-      <c r="AW43" s="77"/>
-      <c r="AX43" s="77"/>
+      <c r="AN43" s="82"/>
+      <c r="AO43" s="82"/>
+      <c r="AP43" s="82"/>
+      <c r="AQ43" s="82"/>
+      <c r="AR43" s="82"/>
+      <c r="AS43" s="82"/>
+      <c r="AT43" s="82"/>
+      <c r="AU43" s="82"/>
+      <c r="AV43" s="82"/>
+      <c r="AW43" s="82"/>
+      <c r="AX43" s="82"/>
     </row>
     <row r="44" spans="1:50">
       <c r="B44" s="25" t="s">
@@ -9465,6 +9379,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="AF2:AL2"/>
+    <mergeCell ref="E2:Y2"/>
+    <mergeCell ref="AM2:AX2"/>
+    <mergeCell ref="AM35:AX35"/>
     <mergeCell ref="AM39:AX39"/>
     <mergeCell ref="AM43:AX43"/>
     <mergeCell ref="AM15:AX15"/>
@@ -9472,11 +9391,6 @@
     <mergeCell ref="AM23:AX23"/>
     <mergeCell ref="AM27:AX27"/>
     <mergeCell ref="AM31:AX31"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="AF2:AL2"/>
-    <mergeCell ref="E2:Y2"/>
-    <mergeCell ref="AM2:AX2"/>
-    <mergeCell ref="AM35:AX35"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
